--- a/resources/templates/exam-timetable.xlsx
+++ b/resources/templates/exam-timetable.xlsx
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">For: who sits it, like ND1, HND2 SWD or Part-time ND2. Empty means everyone.</t>
+          <t xml:space="preserve">For: who sits it, like ND1, HND2 SWD or Part-time ND2; empty means everyone. Venue can stay empty until it's known.</t>
         </is>
       </c>
     </row>
